--- a/src/data.xlsx
+++ b/src/data.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="58">
   <si>
     <t>Team Name</t>
   </si>
@@ -116,6 +116,75 @@
   </si>
   <si>
     <t>2025-08-13T08:43:03.223Z</t>
+  </si>
+  <si>
+    <t>Automated Test Team</t>
+  </si>
+  <si>
+    <t>Auto Tester</t>
+  </si>
+  <si>
+    <t>9876543210</t>
+  </si>
+  <si>
+    <t>auto@test.example</t>
+  </si>
+  <si>
+    <t>Auto College</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>https://github.com/auto</t>
+  </si>
+  <si>
+    <t>X,Y</t>
+  </si>
+  <si>
+    <t>Testing via script</t>
+  </si>
+  <si>
+    <t>uploads\Automated_Test_Team_1755108825839.pdf</t>
+  </si>
+  <si>
+    <t>2025-08-13T18:13:46.005Z</t>
+  </si>
+  <si>
+    <t>uploads\Automated_Test_Team_1755109236611.pdf</t>
+  </si>
+  <si>
+    <t>2025-08-13T18:20:36.653Z</t>
+  </si>
+  <si>
+    <t>uploads\Automated_Test_Team_1755109639722.pdf</t>
+  </si>
+  <si>
+    <t>2025-08-13T18:27:19.781Z</t>
+  </si>
+  <si>
+    <t>Rohit Wakade</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>9307719509</t>
+  </si>
+  <si>
+    <t>rohit.wakade24@vit.edu</t>
+  </si>
+  <si>
+    <t>uploads\Rohit_Wakade_1755114741082.pptx</t>
+  </si>
+  <si>
+    <t>2025-08-13T19:52:21.282Z</t>
+  </si>
+  <si>
+    <t>..\uploads\Automated_Test_Team_1755116497960.pdf</t>
+  </si>
+  <si>
+    <t>2025-08-13T20:21:38.026Z</t>
   </si>
 </sst>
 </file>
@@ -492,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -693,6 +762,256 @@
       </c>
       <c r="P4" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" t="s">
+        <v>44</v>
+      </c>
+      <c r="P5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" t="s">
+        <v>46</v>
+      </c>
+      <c r="P6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L7" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" t="s">
+        <v>50</v>
+      </c>
+      <c r="L8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" t="s">
+        <v>54</v>
+      </c>
+      <c r="P8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J9" t="s">
+        <v>25</v>
+      </c>
+      <c r="K9" t="s">
+        <v>42</v>
+      </c>
+      <c r="L9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" t="s">
+        <v>56</v>
+      </c>
+      <c r="P9" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/src/data.xlsx
+++ b/src/data.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="60">
   <si>
     <t>Team Name</t>
   </si>
@@ -185,6 +185,12 @@
   </si>
   <si>
     <t>2025-08-13T20:21:38.026Z</t>
+  </si>
+  <si>
+    <t>..\uploads\Automated_Test_Team_1755148717515.pdf</t>
+  </si>
+  <si>
+    <t>2025-08-14T05:18:37.648Z</t>
   </si>
 </sst>
 </file>
@@ -561,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -1012,6 +1018,56 @@
       </c>
       <c r="P9" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" t="s">
+        <v>41</v>
+      </c>
+      <c r="J10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" t="s">
+        <v>42</v>
+      </c>
+      <c r="L10" t="s">
+        <v>43</v>
+      </c>
+      <c r="M10" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" t="s">
+        <v>58</v>
+      </c>
+      <c r="P10" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
